--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,100 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45200</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44927</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44836</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>672100</v>
+      </c>
+      <c r="E8" s="3">
         <v>528000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>665300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>774900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>805800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>653300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>771900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>758500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>611600</v>
+      </c>
+      <c r="E9" s="3">
         <v>514700</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
@@ -768,17 +775,20 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E10" s="3">
         <v>13300</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
@@ -797,8 +807,11 @@
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +823,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +853,11 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,8 +885,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,16 +917,19 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>7900</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
+      <c r="E15" s="3">
+        <v>7900</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>5</v>
@@ -926,8 +949,11 @@
       <c r="K15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,17 +962,18 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>638900</v>
+      </c>
+      <c r="E17" s="3">
         <v>550000</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
@@ -965,17 +992,20 @@
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22000</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
@@ -994,8 +1024,11 @@
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,17 +1040,18 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1036,17 +1070,20 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E21" s="3">
         <v>12400</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1065,17 +1102,20 @@
       <c r="K21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E22" s="3">
         <v>24100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1094,17 +1134,20 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-46000</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1123,17 +1166,20 @@
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-20800</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1152,8 +1198,11 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,17 +1230,20 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25200</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1210,17 +1262,20 @@
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25100</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1239,8 +1294,11 @@
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1326,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1358,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1390,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,17 +1422,20 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1384,17 +1454,20 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25100</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1413,8 +1486,11 @@
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,17 +1518,20 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25100</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F35" s="3" t="s">
         <v>5</v>
       </c>
@@ -1471,42 +1550,48 @@
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44927</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44836</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1603,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,17 +1617,18 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E41" s="3">
         <v>18400</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F41" s="3" t="s">
         <v>5</v>
       </c>
@@ -1560,8 +1647,11 @@
       <c r="K41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1589,17 +1679,20 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>627300</v>
+      </c>
+      <c r="E43" s="3">
         <v>545600</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
@@ -1618,8 +1711,11 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1647,17 +1743,20 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E45" s="3">
         <v>49000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
@@ -1676,17 +1775,20 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>723700</v>
+      </c>
+      <c r="E46" s="3">
         <v>613000</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F46" s="3" t="s">
         <v>5</v>
       </c>
@@ -1705,8 +1807,11 @@
       <c r="K46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1734,17 +1839,20 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>685300</v>
+      </c>
+      <c r="E48" s="3">
         <v>696600</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
@@ -1763,17 +1871,20 @@
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>727800</v>
+      </c>
+      <c r="E49" s="3">
         <v>735600</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F49" s="3" t="s">
         <v>5</v>
       </c>
@@ -1792,8 +1903,11 @@
       <c r="K49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +1935,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,17 +1967,20 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E52" s="3">
         <v>74200</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
@@ -1879,8 +1999,11 @@
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,17 +2031,20 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2221600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2119300</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F54" s="3" t="s">
         <v>5</v>
       </c>
@@ -1937,8 +2063,11 @@
       <c r="K54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2079,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,17 +2093,18 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E57" s="3">
         <v>114600</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
@@ -1992,17 +2123,20 @@
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E58" s="3">
         <v>62000</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>5</v>
       </c>
@@ -2021,17 +2155,20 @@
       <c r="K58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E59" s="3">
         <v>263600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2050,17 +2187,20 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>353500</v>
+      </c>
+      <c r="E60" s="3">
         <v>440200</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F60" s="3" t="s">
         <v>5</v>
       </c>
@@ -2079,17 +2219,20 @@
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1029700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1168200</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -2108,17 +2251,20 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E62" s="3">
         <v>308600</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>5</v>
       </c>
@@ -2137,8 +2283,11 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2315,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2347,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,17 +2379,20 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1691200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1921500</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F66" s="3" t="s">
         <v>5</v>
       </c>
@@ -2253,8 +2411,11 @@
       <c r="K66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2427,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2457,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2489,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2521,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,17 +2553,20 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-157300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-169000</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F72" s="3" t="s">
         <v>5</v>
       </c>
@@ -2411,8 +2585,11 @@
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2617,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2649,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,17 +2681,20 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>530400</v>
+      </c>
+      <c r="E76" s="3">
         <v>197800</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F76" s="3" t="s">
         <v>5</v>
       </c>
@@ -2527,8 +2713,11 @@
       <c r="K76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,51 +2745,57 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45200</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44927</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44836</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25100</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
@@ -2619,8 +2814,11 @@
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,17 +2830,18 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E83" s="3">
         <v>34300</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
@@ -2661,8 +2860,11 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +2892,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +2924,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +2956,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +2988,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,17 +3020,20 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-54200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22200</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
@@ -2835,8 +3052,11 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,13 +3068,14 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-22700</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -2877,8 +3098,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3130,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,17 +3162,20 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28900</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>5</v>
       </c>
@@ -2964,8 +3194,11 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3210,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3240,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3272,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3304,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,17 +3336,20 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E100" s="3">
         <v>36300</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
@@ -3122,17 +3368,20 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>5</v>
       </c>
@@ -3151,17 +3400,20 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15000</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F102" s="3" t="s">
         <v>5</v>
       </c>
@@ -3178,6 +3430,9 @@
         <v>5</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,45 +656,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45200</v>
@@ -703,30 +705,33 @@
         <v>45109</v>
       </c>
       <c r="I7" s="2">
-        <v>45018</v>
-      </c>
-      <c r="J7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="2">
         <v>44927</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44836</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>720100</v>
+      </c>
+      <c r="E8" s="3">
         <v>672100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>528000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>665300</v>
       </c>
       <c r="G8" s="3">
         <v>774900</v>
@@ -737,37 +742,40 @@
       <c r="I8" s="3">
         <v>653300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>771900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>758500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>644300</v>
+      </c>
+      <c r="E9" s="3">
         <v>611600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>514700</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
+      <c r="G9" s="3">
+        <v>687300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>715800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>611300</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>5</v>
@@ -778,28 +786,31 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E10" s="3">
         <v>60500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13300</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
+      <c r="G10" s="3">
+        <v>87600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>90000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>41900</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>5</v>
@@ -810,8 +821,11 @@
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +838,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,8 +871,11 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,31 +906,34 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -920,31 +941,34 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>7900</v>
+        <v>6700</v>
       </c>
       <c r="E15" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -952,8 +976,11 @@
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -963,28 +990,29 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>678100</v>
+      </c>
+      <c r="E17" s="3">
         <v>638900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>550000</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
+      <c r="G17" s="3">
+        <v>721900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>752600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>641600</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>5</v>
@@ -995,28 +1023,31 @@
       <c r="L17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>33200</v>
+        <v>41900</v>
       </c>
       <c r="E18" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
+        <v>33100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>53000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>53200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>11700</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
@@ -1027,8 +1058,11 @@
       <c r="L18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1041,29 +1075,30 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1073,31 +1108,34 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>68200</v>
+        <v>48700</v>
       </c>
       <c r="E21" s="3">
-        <v>12400</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+        <v>40500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>59700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>60800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1105,28 +1143,31 @@
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>22600</v>
+        <v>22400</v>
       </c>
       <c r="E22" s="3">
-        <v>24100</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
+        <v>21300</v>
+      </c>
+      <c r="F22" s="3">
+        <v>22800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>23200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>21100</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>5</v>
@@ -1137,28 +1178,31 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E23" s="3">
         <v>11200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-46000</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
+      <c r="G23" s="3">
+        <v>26900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>29600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-11300</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>5</v>
@@ -1169,28 +1213,31 @@
       <c r="L23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-20800</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
+      <c r="G24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-4200</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>5</v>
@@ -1201,8 +1248,11 @@
       <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1233,28 +1283,31 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E26" s="3">
         <v>11700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25200</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
+      <c r="G26" s="3">
+        <v>16900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-7100</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>5</v>
@@ -1265,28 +1318,31 @@
       <c r="L26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>11700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25100</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
+      <c r="G27" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-8800</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>5</v>
@@ -1297,8 +1353,11 @@
       <c r="L27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1329,8 +1388,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,8 +1423,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1393,8 +1458,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1425,29 +1493,32 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1457,28 +1528,31 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>11700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25100</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
+      <c r="G33" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-8800</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>5</v>
@@ -1489,8 +1563,11 @@
       <c r="L33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1521,28 +1598,31 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>11700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25100</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
+      <c r="G35" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-8800</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>5</v>
@@ -1553,24 +1633,27 @@
       <c r="L35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45200</v>
@@ -1579,19 +1662,22 @@
         <v>45109</v>
       </c>
       <c r="I38" s="2">
-        <v>45018</v>
-      </c>
-      <c r="J38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="2">
         <v>44927</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44836</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1604,8 +1690,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1618,20 +1705,21 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E41" s="3">
         <v>30900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>5</v>
       </c>
@@ -1650,8 +1738,11 @@
       <c r="L41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1682,20 +1773,23 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>541600</v>
+      </c>
+      <c r="E43" s="3">
         <v>627300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>545600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
@@ -1714,31 +1808,34 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1746,16 +1843,19 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>65500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>49000</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
@@ -1778,20 +1878,23 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>634600</v>
+      </c>
+      <c r="E46" s="3">
         <v>723700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>613000</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>5</v>
       </c>
@@ -1810,31 +1913,34 @@
       <c r="L46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1842,20 +1948,23 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>644100</v>
+      </c>
+      <c r="E48" s="3">
         <v>685300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>696600</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
@@ -1874,28 +1983,31 @@
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>722600</v>
+      </c>
+      <c r="E49" s="3">
         <v>727800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>735600</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -1906,8 +2018,11 @@
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1938,8 +2053,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1970,19 +2088,22 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>84900</v>
+        <v>83900</v>
       </c>
       <c r="E52" s="3">
-        <v>74200</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+        <v>55700</v>
+      </c>
+      <c r="F52" s="3">
+        <v>53400</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
@@ -2002,8 +2123,11 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2034,20 +2158,23 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2112700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2221600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2119300</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>5</v>
       </c>
@@ -2066,8 +2193,11 @@
       <c r="L54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2080,8 +2210,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2094,20 +2225,21 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E57" s="3">
         <v>116600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>114600</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2126,28 +2258,31 @@
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>51600</v>
+        <v>69300</v>
       </c>
       <c r="E58" s="3">
-        <v>62000</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>71200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>81900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -2158,19 +2293,22 @@
       <c r="L58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>185300</v>
+        <v>21900</v>
       </c>
       <c r="E59" s="3">
-        <v>263600</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
+        <v>17200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>109800</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
@@ -2190,20 +2328,23 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>386200</v>
+      </c>
+      <c r="E60" s="3">
         <v>353500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>440200</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>5</v>
       </c>
@@ -2222,19 +2363,22 @@
       <c r="L60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1029700</v>
+        <v>992300</v>
       </c>
       <c r="E61" s="3">
-        <v>1168200</v>
+        <v>1129000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1272300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2254,19 +2398,22 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>304000</v>
+        <v>67900</v>
       </c>
       <c r="E62" s="3">
-        <v>308600</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
+        <v>69900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>69600</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
@@ -2286,8 +2433,11 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2318,8 +2468,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2350,8 +2503,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2382,19 +2538,22 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1691200</v>
+        <v>1581300</v>
       </c>
       <c r="E66" s="3">
-        <v>1921500</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>5</v>
+        <v>1687200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1917000</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>5</v>
@@ -2414,8 +2573,11 @@
       <c r="L66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2428,8 +2590,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2460,8 +2623,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2492,8 +2658,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2524,8 +2693,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2556,20 +2728,23 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-161000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-157300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-169000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
@@ -2588,8 +2763,11 @@
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2620,8 +2798,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2652,8 +2833,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2684,28 +2868,31 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>527300</v>
+      </c>
+      <c r="E76" s="3">
         <v>530400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>197800</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
+      <c r="I76" s="3">
+        <v>386800</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -2716,8 +2903,11 @@
       <c r="L76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2748,24 +2938,27 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45200</v>
@@ -2774,39 +2967,42 @@
         <v>45109</v>
       </c>
       <c r="I80" s="2">
-        <v>45018</v>
-      </c>
-      <c r="J80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K80" s="2">
         <v>44927</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44836</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>11700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25100</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
+      <c r="G81" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-8800</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>5</v>
@@ -2817,8 +3013,11 @@
       <c r="L81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2831,16 +3030,17 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>34400</v>
+        <v>33900</v>
       </c>
       <c r="E83" s="3">
-        <v>34300</v>
+        <v>34900</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
@@ -2863,8 +3063,11 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2895,8 +3098,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2927,8 +3133,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2959,8 +3168,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2991,8 +3203,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3023,28 +3238,31 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-54200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22200</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
+      <c r="G89" s="3">
+        <v>81300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-71400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>51900</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>5</v>
@@ -3055,8 +3273,11 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3069,31 +3290,32 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22700</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-30500</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-25900</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-30500</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-23200</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3101,8 +3323,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3133,8 +3358,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3165,28 +3393,31 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28900</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
+      <c r="G94" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-20600</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>5</v>
@@ -3197,8 +3428,11 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3211,31 +3445,32 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3243,8 +3478,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3275,8 +3513,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3307,8 +3548,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3339,28 +3583,31 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-141800</v>
+      </c>
+      <c r="E100" s="3">
         <v>86800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
+      <c r="G100" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>110100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-79400</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>5</v>
@@ -3371,16 +3618,19 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>5</v>
@@ -3403,36 +3653,42 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E102" s="3">
         <v>12500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15000</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
+      <c r="G102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,130 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44836</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>717100</v>
+      </c>
+      <c r="E8" s="3">
         <v>720100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>672100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>528000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>665300</v>
+      </c>
+      <c r="I8" s="3">
         <v>774900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>805800</v>
       </c>
-      <c r="I8" s="3">
-        <v>653300</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
         <v>771900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>758500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>646000</v>
+      </c>
+      <c r="E9" s="3">
         <v>644300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>611600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>514700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>611400</v>
+      </c>
+      <c r="I9" s="3">
         <v>687300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>715800</v>
       </c>
-      <c r="I9" s="3">
-        <v>611300</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
@@ -789,32 +795,35 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E10" s="3">
         <v>75800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>53900</v>
+      </c>
+      <c r="I10" s="3">
         <v>87600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>90000</v>
       </c>
-      <c r="I10" s="3">
-        <v>41900</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
@@ -824,8 +833,11 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -839,8 +851,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -874,8 +887,11 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,13 +925,16 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>11800</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -926,8 +945,8 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3">
+        <v>221400</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
@@ -935,8 +954,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -944,8 +963,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -968,10 +990,10 @@
         <v>6700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
@@ -979,8 +1001,11 @@
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -991,32 +1016,33 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>673400</v>
+      </c>
+      <c r="E17" s="3">
         <v>678100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>638900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>550000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>639400</v>
+      </c>
+      <c r="I17" s="3">
         <v>721900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>752600</v>
       </c>
-      <c r="I17" s="3">
-        <v>641600</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1026,32 +1052,35 @@
       <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E18" s="3">
         <v>41900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>25900</v>
+      </c>
+      <c r="I18" s="3">
         <v>53000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>53200</v>
       </c>
-      <c r="I18" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1061,8 +1090,11 @@
       <c r="M18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1076,32 +1108,33 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
-        <v>700</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1111,34 +1144,37 @@
       <c r="M20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E21" s="3">
         <v>48700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>32300</v>
+      </c>
+      <c r="I21" s="3">
         <v>59700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>60800</v>
       </c>
-      <c r="I21" s="3">
-        <v>17700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
@@ -1146,32 +1182,35 @@
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E22" s="3">
         <v>22400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I22" s="3">
         <v>24800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>23200</v>
       </c>
-      <c r="I22" s="3">
-        <v>21100</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1181,32 +1220,35 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E23" s="3">
         <v>18200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-46000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-220200</v>
+      </c>
+      <c r="I23" s="3">
         <v>26900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>29600</v>
       </c>
-      <c r="I23" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1216,32 +1258,35 @@
       <c r="M23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E24" s="3">
         <v>21800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="I24" s="3">
         <v>10000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>11000</v>
       </c>
-      <c r="I24" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1251,8 +1296,11 @@
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1286,32 +1334,35 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-212800</v>
+      </c>
+      <c r="I26" s="3">
         <v>16900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>18500</v>
       </c>
-      <c r="I26" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1321,32 +1372,35 @@
       <c r="M26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="I27" s="3">
         <v>16200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>17100</v>
       </c>
-      <c r="I27" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1356,8 +1410,11 @@
       <c r="M27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1391,8 +1448,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1426,8 +1486,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1461,8 +1524,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1496,32 +1562,35 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1531,32 +1600,35 @@
       <c r="M32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="I33" s="3">
         <v>16200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>17100</v>
       </c>
-      <c r="I33" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1566,8 +1638,11 @@
       <c r="M33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1601,32 +1676,35 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="I35" s="3">
         <v>16200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>17100</v>
       </c>
-      <c r="I35" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
@@ -1636,48 +1714,54 @@
       <c r="M35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44836</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1691,8 +1775,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1706,25 +1791,26 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E41" s="3">
         <v>52500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18400</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
+      <c r="H41" s="3">
+        <v>33400</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>5</v>
@@ -1741,8 +1827,11 @@
       <c r="M41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1776,25 +1865,28 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>519600</v>
+      </c>
+      <c r="E43" s="3">
         <v>541600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>627300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>545600</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
+      <c r="H43" s="3">
+        <v>617300</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
@@ -1811,8 +1903,11 @@
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1837,8 +1932,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1846,8 +1941,11 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1881,25 +1979,28 @@
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>601400</v>
+      </c>
+      <c r="E46" s="3">
         <v>634600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>723700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>613000</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>5</v>
+      <c r="H46" s="3">
+        <v>682900</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>5</v>
@@ -1916,13 +2017,16 @@
       <c r="M46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>10900</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
@@ -1933,8 +2037,8 @@
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
+      <c r="H47" s="3">
+        <v>11900</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
@@ -1942,8 +2046,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -1951,25 +2055,28 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>649200</v>
+      </c>
+      <c r="E48" s="3">
         <v>644100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>685300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>696600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
+      <c r="H48" s="3">
+        <v>707400</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
@@ -1986,31 +2093,34 @@
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>709200</v>
+      </c>
+      <c r="E49" s="3">
         <v>722600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>727800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>735600</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>744900</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -2021,8 +2131,11 @@
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2056,8 +2169,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2091,25 +2207,28 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E52" s="3">
         <v>83900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>53400</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
+      <c r="H52" s="3">
+        <v>38500</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -2126,8 +2245,11 @@
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2161,25 +2283,28 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2074400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2112700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2221600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2119300</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>5</v>
+      <c r="H54" s="3">
+        <v>2189900</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>5</v>
@@ -2196,8 +2321,11 @@
       <c r="M54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2211,8 +2339,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2226,25 +2355,26 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E57" s="3">
         <v>121300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>116600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>114600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
+      <c r="H57" s="3">
+        <v>116600</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
@@ -2261,31 +2391,34 @@
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E58" s="3">
         <v>69300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>71200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>81900</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>86600</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -2296,25 +2429,28 @@
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>109800</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
+      <c r="H59" s="3">
+        <v>43700</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -2331,25 +2467,28 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E60" s="3">
         <v>386200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>353500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>440200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>5</v>
+      <c r="H60" s="3">
+        <v>420600</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>5</v>
@@ -2366,25 +2505,28 @@
       <c r="M60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>950600</v>
+      </c>
+      <c r="E61" s="3">
         <v>992300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1129000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1272300</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1237800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2401,25 +2543,28 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E62" s="3">
         <v>67900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>69900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>69600</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
+      <c r="H62" s="3">
+        <v>71100</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>5</v>
@@ -2436,8 +2581,11 @@
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2471,8 +2619,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2506,8 +2657,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2541,25 +2695,28 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1514200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1581300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1687200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1917000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
+      <c r="H66" s="3">
+        <v>1864700</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>5</v>
@@ -2576,8 +2733,11 @@
       <c r="M66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2591,8 +2751,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2626,8 +2787,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2661,8 +2825,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2696,8 +2863,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2731,25 +2901,28 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-150700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-161000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-157300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-169000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
+      <c r="H72" s="3">
+        <v>-144100</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
@@ -2766,8 +2939,11 @@
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2801,8 +2977,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2836,8 +3015,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2871,28 +3053,31 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>555600</v>
+      </c>
+      <c r="E76" s="3">
         <v>527300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>530400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>197800</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="3">
-        <v>386800</v>
+      <c r="H76" s="3">
+        <v>226000</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -2906,8 +3091,11 @@
       <c r="M76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2941,72 +3129,78 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44836</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="I81" s="3">
         <v>16200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>17100</v>
       </c>
-      <c r="I81" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
@@ -3016,8 +3210,11 @@
       <c r="M81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3031,23 +3228,24 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>34700</v>
+      </c>
+      <c r="F83" s="3">
         <v>33900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>34900</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3066,8 +3264,11 @@
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3101,8 +3302,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3136,8 +3340,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3171,8 +3378,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3206,8 +3416,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3241,32 +3454,35 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E89" s="3">
         <v>173600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-54200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>105700</v>
+      </c>
+      <c r="I89" s="3">
         <v>81300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-71400</v>
       </c>
-      <c r="I89" s="3">
-        <v>51900</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3276,8 +3492,11 @@
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3291,34 +3510,35 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-25900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-30500</v>
       </c>
-      <c r="I91" s="3">
-        <v>-23200</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3326,8 +3546,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3361,8 +3584,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3396,32 +3622,35 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-22800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-28600</v>
       </c>
-      <c r="I94" s="3">
-        <v>-20600</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3431,8 +3660,11 @@
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3446,8 +3678,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3472,8 +3705,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3481,8 +3714,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3516,8 +3752,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3551,8 +3790,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3586,32 +3828,35 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-141800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>86800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-82000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-52200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>110100</v>
       </c>
-      <c r="I100" s="3">
-        <v>-79400</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
@@ -3621,8 +3866,11 @@
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3630,14 +3878,14 @@
         <v>200</v>
       </c>
       <c r="E101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>200</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
       </c>
@@ -3656,39 +3904,45 @@
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
         <v>21500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I102" s="3">
         <v>6100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>10400</v>
       </c>
-      <c r="I102" s="3">
-        <v>-47900</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,139 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44836</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>550100</v>
+      </c>
+      <c r="E8" s="3">
         <v>717100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>720100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>672100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>528000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>665300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>774900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>805800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>771900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>758500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>529800</v>
+      </c>
+      <c r="E9" s="3">
         <v>646000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>644300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>611600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>514700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>611400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>687300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>715800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -798,35 +805,38 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E10" s="3">
         <v>71100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>75800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>60500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>53900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>87600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>90000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -836,8 +846,11 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,8 +865,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -890,8 +904,11 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,17 +945,20 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>11800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -946,19 +966,19 @@
         <v>5</v>
       </c>
       <c r="H14" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I14" s="3">
         <v>221400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -966,8 +986,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -993,10 +1016,10 @@
         <v>6700</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
@@ -1004,8 +1027,11 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,35 +1043,36 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>562800</v>
+      </c>
+      <c r="E17" s="3">
         <v>673400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>678100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>638900</v>
       </c>
-      <c r="G17" s="3">
-        <v>550000</v>
-      </c>
       <c r="H17" s="3">
+        <v>541600</v>
+      </c>
+      <c r="I17" s="3">
         <v>639400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>721900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>752600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1055,35 +1082,38 @@
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E18" s="3">
         <v>43700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>41900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-21900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="I18" s="3">
         <v>25900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>53000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>53200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1093,8 +1123,11 @@
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,8 +1142,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1118,26 +1152,26 @@
         <v>500</v>
       </c>
       <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1147,37 +1181,40 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E21" s="3">
         <v>49800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>48700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-15200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I21" s="3">
         <v>32300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>59700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>60800</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
@@ -1185,35 +1222,38 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E22" s="3">
         <v>16900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1223,35 +1263,38 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="E23" s="3">
         <v>13300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-46000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-220200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1261,35 +1304,38 @@
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E24" s="3">
         <v>2900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-20800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11000</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1299,8 +1345,11 @@
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,35 +1386,38 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E26" s="3">
         <v>10300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-212800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1375,35 +1427,38 @@
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E27" s="3">
         <v>10300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-210700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1413,8 +1468,11 @@
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1509,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1550,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1591,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,8 +1632,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1574,26 +1644,26 @@
         <v>-500</v>
       </c>
       <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1603,35 +1673,38 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E33" s="3">
         <v>10300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-210700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1641,8 +1714,11 @@
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,35 +1755,38 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E35" s="3">
         <v>10300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-210700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>5</v>
       </c>
@@ -1717,51 +1796,57 @@
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44836</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +1861,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,29 +1878,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E41" s="3">
         <v>49000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33400</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
       </c>
@@ -1830,8 +1917,11 @@
       <c r="N41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1868,29 +1958,32 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>479700</v>
+      </c>
+      <c r="E43" s="3">
         <v>519600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>541600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>627300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>545600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>617300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
@@ -1906,8 +1999,11 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1935,8 +2031,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1944,8 +2040,11 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1982,29 +2081,32 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>536100</v>
+      </c>
+      <c r="E46" s="3">
         <v>601400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>634600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>723700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>613000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>682900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2020,37 +2122,40 @@
       <c r="N46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>10900</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>11900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2058,29 +2163,32 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>640600</v>
+      </c>
+      <c r="E48" s="3">
         <v>649200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>644100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>685300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>696600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>707400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2096,34 +2204,37 @@
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>702700</v>
+      </c>
+      <c r="E49" s="3">
         <v>709200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>722600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>727800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>735600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>744900</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
@@ -2134,8 +2245,11 @@
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2286,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,29 +2327,32 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E52" s="3">
         <v>100700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>53400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2248,8 +2368,11 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,29 +2409,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1992600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2074400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2112700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2221600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2119300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2189900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
       </c>
@@ -2324,8 +2450,11 @@
       <c r="N54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2469,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,29 +2486,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E57" s="3">
         <v>125700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>121300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>116600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>114600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>116600</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2394,34 +2525,37 @@
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E58" s="3">
         <v>73200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>69300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>71200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>81900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>86600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>5</v>
@@ -2432,29 +2566,32 @@
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E59" s="3">
         <v>25000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>109800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>43700</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2470,29 +2607,32 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>340500</v>
+      </c>
+      <c r="E60" s="3">
         <v>382300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>386200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>353500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>440200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>420600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
@@ -2508,29 +2648,32 @@
       <c r="N60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>930300</v>
+      </c>
+      <c r="E61" s="3">
         <v>950600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>992300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1129000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1272300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1237800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2546,29 +2689,32 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E62" s="3">
         <v>66100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>67900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>69900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>69600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>71100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
@@ -2584,8 +2730,11 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +2771,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +2812,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,29 +2853,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1451400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1514200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1581300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1687200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1917000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1864700</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
@@ -2736,8 +2894,11 @@
       <c r="N66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +2913,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +2952,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +2993,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2866,8 +3034,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,29 +3075,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-168700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-150700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-161000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-157300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-169000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-144100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
@@ -2942,8 +3116,11 @@
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3157,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3198,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,29 +3239,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>536500</v>
+      </c>
+      <c r="E76" s="3">
         <v>555600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>527300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>530400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>197800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>226000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
       </c>
@@ -3094,8 +3280,11 @@
       <c r="N76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,78 +3321,84 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44836</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E81" s="3">
         <v>10300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-210700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>5</v>
       </c>
@@ -3213,8 +3408,11 @@
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,26 +3427,27 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E83" s="3">
         <v>32600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>34900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3267,8 +3466,11 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3507,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3548,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +3589,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +3630,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,35 +3671,38 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E89" s="3">
         <v>61000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>173600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-54200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-22200</v>
-      </c>
       <c r="H89" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="I89" s="3">
         <v>105700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>81300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-71400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3495,8 +3712,11 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,37 +3731,38 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-30500</v>
       </c>
-      <c r="H91" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-25900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-30500</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3549,8 +3770,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +3811,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,35 +3852,38 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-28900</v>
-      </c>
       <c r="H94" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-22900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3663,8 +3893,11 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,8 +3912,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3708,8 +3942,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3717,8 +3951,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +3992,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4033,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,35 +4074,38 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-33900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-141800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>86800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>36300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-82000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-52200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>110100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
@@ -3869,26 +4115,29 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>5</v>
       </c>
@@ -3907,42 +4156,48 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10400</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,149 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
         <v>44927</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44836</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>724100</v>
+      </c>
+      <c r="E8" s="3">
         <v>550100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>717100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>720100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>672100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>528000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>665300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>774900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>805800</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3">
         <v>771900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>758500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>656300</v>
+      </c>
+      <c r="E9" s="3">
         <v>529800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>646000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>644300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>611600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>514700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>611400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>687300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>715800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -808,38 +815,41 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E10" s="3">
         <v>20300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>71100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>75800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>60500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>53900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>87600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>90000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -849,8 +859,11 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -866,8 +879,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,8 +921,11 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,40 +965,43 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>11800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3">
+        <v>300</v>
+      </c>
+      <c r="I14" s="3">
         <v>8300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>221400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -989,8 +1009,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,10 +1042,10 @@
         <v>6700</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
@@ -1030,8 +1053,11 @@
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,38 +1070,39 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>691900</v>
+      </c>
+      <c r="E17" s="3">
         <v>562800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>673400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>678100</v>
       </c>
-      <c r="G17" s="3">
-        <v>638900</v>
-      </c>
       <c r="H17" s="3">
+        <v>638600</v>
+      </c>
+      <c r="I17" s="3">
         <v>541600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>639400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>721900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>752600</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1085,38 +1112,41 @@
       <c r="O17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41900</v>
       </c>
-      <c r="G18" s="3">
-        <v>33100</v>
-      </c>
       <c r="H18" s="3">
+        <v>33500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-13600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>53000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1126,8 +1156,11 @@
       <c r="O18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1143,38 +1176,39 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>500</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
         <v>500</v>
       </c>
       <c r="F20" s="3">
+        <v>500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1184,40 +1218,43 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>49800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>48700</v>
       </c>
-      <c r="G21" s="3">
-        <v>40500</v>
-      </c>
       <c r="H21" s="3">
+        <v>40800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>59700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>60800</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
+      <c r="M21" s="3">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
@@ -1225,38 +1262,41 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E22" s="3">
         <v>16700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>21300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1266,38 +1306,41 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-31100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-46000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-220200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>26900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1307,38 +1350,41 @@
       <c r="O23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-13100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-20800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1348,8 +1394,11 @@
       <c r="O24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1389,38 +1438,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-212800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18500</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1430,38 +1482,41 @@
       <c r="O26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-210700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1471,8 +1526,11 @@
       <c r="O27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1512,8 +1570,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1614,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1594,8 +1658,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,38 +1702,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-500</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
         <v>-500</v>
       </c>
       <c r="F32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1676,38 +1746,41 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-210700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1717,8 +1790,11 @@
       <c r="O33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1758,38 +1834,41 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-210700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>5</v>
       </c>
@@ -1799,54 +1878,60 @@
       <c r="O35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N38" s="2">
         <v>44927</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44836</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1862,8 +1947,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1879,32 +1965,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E41" s="3">
         <v>15300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33400</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
       </c>
@@ -1920,8 +2007,11 @@
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1961,32 +2051,35 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>570600</v>
+      </c>
+      <c r="E43" s="3">
         <v>479700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>519600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>541600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>627300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>545600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>617300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2002,8 +2095,11 @@
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2034,8 +2130,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2043,8 +2139,11 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2084,32 +2183,35 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>651900</v>
+      </c>
+      <c r="E46" s="3">
         <v>536100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>601400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>634600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>723700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>613000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>682900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2125,40 +2227,43 @@
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>10900</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>11900</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2166,32 +2271,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>639900</v>
+      </c>
+      <c r="E48" s="3">
         <v>640600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>649200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>644100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>685300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>696600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>707400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2207,37 +2315,40 @@
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>701500</v>
+      </c>
+      <c r="E49" s="3">
         <v>702700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>709200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>722600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>727800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>735600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>744900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
@@ -2248,8 +2359,11 @@
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2289,8 +2403,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2330,32 +2447,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E52" s="3">
         <v>85800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>100700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>83900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>53400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2371,8 +2491,11 @@
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2412,32 +2535,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2107800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1992600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2074400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2112700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2221600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2119300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2189900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
       </c>
@@ -2453,8 +2579,11 @@
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2470,8 +2599,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2487,32 +2617,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E57" s="3">
         <v>116000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>125700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>121300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>116600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>114600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2528,37 +2659,40 @@
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E58" s="3">
         <v>63700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>73200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>71200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>81900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>86600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
@@ -2569,32 +2703,35 @@
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E59" s="3">
         <v>25400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>109800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>43700</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2610,32 +2747,35 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>379500</v>
+      </c>
+      <c r="E60" s="3">
         <v>340500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>382300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>386200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>353500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>440200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>420600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
@@ -2651,32 +2791,35 @@
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>995200</v>
+      </c>
+      <c r="E61" s="3">
         <v>930300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>950600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>992300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1129000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1272300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1237800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2692,32 +2835,35 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E62" s="3">
         <v>65400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>67900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>69900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>71100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
@@ -2733,8 +2879,11 @@
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2774,8 +2923,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2967,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2856,32 +3011,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1535900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1451400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1514200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1581300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1687200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1917000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1864700</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
       </c>
@@ -2897,8 +3055,11 @@
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,8 +3075,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2955,8 +3117,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2996,8 +3161,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3037,8 +3205,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3078,32 +3249,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-160700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-168700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-150700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-161000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-157300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-169000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-144100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3119,8 +3293,11 @@
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3160,8 +3337,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3201,8 +3381,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3242,32 +3425,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>567100</v>
+      </c>
+      <c r="E76" s="3">
         <v>536500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>555600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>527300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>530400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>197800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>226000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
       </c>
@@ -3283,8 +3469,11 @@
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3324,84 +3513,90 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N80" s="2">
         <v>44927</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44836</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-210700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>5</v>
       </c>
@@ -3411,8 +3606,11 @@
       <c r="O81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3428,8 +3626,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3437,20 +3636,20 @@
         <v>32800</v>
       </c>
       <c r="E83" s="3">
+        <v>32800</v>
+      </c>
+      <c r="F83" s="3">
         <v>32600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3469,8 +3668,11 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3510,8 +3712,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3756,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3592,8 +3800,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3633,8 +3844,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3674,38 +3888,41 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E89" s="3">
         <v>16700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>61000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>173600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-54200</v>
-      </c>
       <c r="H89" s="3">
+        <v>-56600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-26500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>105700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>81300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-71400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3715,8 +3932,11 @@
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3732,40 +3952,41 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-22700</v>
-      </c>
       <c r="H91" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-26300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3773,8 +3994,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3814,8 +4038,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3855,38 +4082,41 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-20000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-24600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3896,8 +4126,11 @@
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3913,8 +4146,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3945,8 +4179,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -3954,8 +4188,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3995,8 +4232,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4036,8 +4276,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4077,38 +4320,41 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-27200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-33900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-141800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>86800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-82000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-52200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>110100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4118,29 +4364,32 @@
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4159,45 +4408,51 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,169 +656,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44836</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>858600</v>
+      </c>
+      <c r="E8" s="3">
         <v>850000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>724100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>550100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>717100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>720100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>672100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>528000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>665300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>774900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>805800</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3">
         <v>771900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>758500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>778100</v>
+      </c>
+      <c r="E9" s="3">
         <v>772100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>656300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>529800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>646000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>644300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>611600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>514700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>611400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>687300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>715800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
@@ -828,44 +834,47 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E10" s="3">
         <v>78000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>67800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>75800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>60500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>53900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>87600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>90000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
@@ -875,8 +884,11 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -894,8 +906,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -941,8 +954,11 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -988,46 +1004,49 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>11800</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>221400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1035,13 +1054,16 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6700</v>
+        <v>7200</v>
       </c>
       <c r="E15" s="3">
         <v>6700</v>
@@ -1071,10 +1093,10 @@
         <v>6700</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>5</v>
@@ -1082,8 +1104,11 @@
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,44 +1123,45 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>819300</v>
+      </c>
+      <c r="E17" s="3">
         <v>811400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>691900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>562800</v>
       </c>
-      <c r="G17" s="3">
-        <v>673400</v>
-      </c>
       <c r="H17" s="3">
+        <v>684000</v>
+      </c>
+      <c r="I17" s="3">
         <v>676200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>638600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>541600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>639400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>721900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>752600</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1145,44 +1171,47 @@
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E18" s="3">
         <v>38700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>32200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12700</v>
       </c>
-      <c r="G18" s="3">
-        <v>43700</v>
-      </c>
       <c r="H18" s="3">
+        <v>33100</v>
+      </c>
+      <c r="I18" s="3">
         <v>43800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>53000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>53200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1192,8 +1221,11 @@
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1211,44 +1243,45 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>500</v>
       </c>
       <c r="G20" s="3">
         <v>500</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1258,46 +1291,49 @@
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E21" s="3">
         <v>45300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6500</v>
       </c>
-      <c r="G21" s="3">
-        <v>49800</v>
-      </c>
       <c r="H21" s="3">
+        <v>39200</v>
+      </c>
+      <c r="I21" s="3">
         <v>50700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>59700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>60800</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
+      <c r="O21" s="3">
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
@@ -1305,44 +1341,47 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E22" s="3">
         <v>25500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>21300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23200</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1352,44 +1391,47 @@
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E23" s="3">
         <v>10000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-220200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29600</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1399,44 +1441,47 @@
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E24" s="3">
         <v>7900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-13100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-20800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1446,8 +1491,11 @@
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1493,44 +1541,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-212800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18500</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1540,44 +1591,47 @@
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-210700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1587,8 +1641,11 @@
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1634,8 +1691,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1681,8 +1741,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1728,8 +1791,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1775,44 +1841,47 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-500</v>
       </c>
       <c r="G32" s="3">
         <v>-500</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1822,44 +1891,47 @@
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-210700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1869,8 +1941,11 @@
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1916,44 +1991,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-210700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>5</v>
       </c>
@@ -1963,60 +2041,66 @@
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44836</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2034,8 +2118,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2053,38 +2138,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E41" s="3">
         <v>16100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2100,8 +2186,11 @@
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2147,38 +2236,41 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>709800</v>
+      </c>
+      <c r="E43" s="3">
         <v>671100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>570600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>479700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>519600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>541600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>627300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>545600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>617300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2194,8 +2286,11 @@
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2232,8 +2327,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2241,8 +2336,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2288,38 +2386,41 @@
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>881400</v>
+      </c>
+      <c r="E46" s="3">
         <v>740500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>651900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>536100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>601400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>634600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>723700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>613000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>682900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2335,13 +2436,16 @@
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>11500</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
@@ -2349,32 +2453,32 @@
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>10900</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>11900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2382,38 +2486,41 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>667700</v>
+      </c>
+      <c r="E48" s="3">
         <v>627400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>639900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>640600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>649200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>644100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>685300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>696600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>707400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2429,43 +2536,46 @@
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>738900</v>
+      </c>
+      <c r="E49" s="3">
         <v>692700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>701500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>702700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>709200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>722600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>727800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>735600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>744900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
@@ -2476,8 +2586,11 @@
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2523,8 +2636,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2570,38 +2686,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E52" s="3">
         <v>84900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>84600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>85800</v>
       </c>
-      <c r="G52" s="3">
-        <v>100700</v>
-      </c>
       <c r="H52" s="3">
+        <v>76800</v>
+      </c>
+      <c r="I52" s="3">
         <v>83900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38500</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2617,8 +2736,11 @@
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2664,38 +2786,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2407700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2177300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2107800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1992600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2074400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2112700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2221600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2119300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2189900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>5</v>
       </c>
@@ -2711,8 +2836,11 @@
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2730,8 +2858,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2749,38 +2878,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E57" s="3">
         <v>146600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>128200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>116000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>125700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>121300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>114600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2796,43 +2926,46 @@
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E58" s="3">
         <v>74200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>68700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>73200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>71200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>81900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>86600</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
@@ -2843,38 +2976,41 @@
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E59" s="3">
         <v>32100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>109800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,38 +3026,41 @@
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>496400</v>
+      </c>
+      <c r="E60" s="3">
         <v>442200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>379500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>340500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>382300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>386200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>353500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>440200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>420600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>5</v>
       </c>
@@ -2937,38 +3076,41 @@
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>870800</v>
+      </c>
+      <c r="E61" s="3">
         <v>995500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>995200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>930300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>950600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>992300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1129000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1272300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1237800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2984,38 +3126,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E62" s="3">
         <v>77100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>65400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>67900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>69900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>69600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>71100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3031,8 +3176,11 @@
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3078,8 +3226,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3125,8 +3276,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3172,38 +3326,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1529300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1587300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1535900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1451400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1514200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1581300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1687200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1917000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1864700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>5</v>
       </c>
@@ -3219,8 +3376,11 @@
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3238,8 +3398,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3285,8 +3446,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3332,8 +3496,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3379,8 +3546,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3426,38 +3596,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-128400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-158600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-160700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-168700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-150700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-161000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-157300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-169000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-144100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3473,8 +3646,11 @@
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3520,8 +3696,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3567,8 +3746,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3614,38 +3796,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>873000</v>
+      </c>
+      <c r="E76" s="3">
         <v>585200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>567100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>536500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>555600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>527300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>530400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>197800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>226000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>5</v>
       </c>
@@ -3661,8 +3846,11 @@
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3708,96 +3896,102 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O80" s="2">
+      <c r="O80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44836</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-210700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>5</v>
       </c>
@@ -3807,8 +4001,11 @@
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3826,35 +4023,36 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E83" s="3">
         <v>31800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>32800</v>
       </c>
       <c r="F83" s="3">
         <v>32800</v>
       </c>
       <c r="G83" s="3">
+        <v>32800</v>
+      </c>
+      <c r="H83" s="3">
         <v>32600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>33900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3873,8 +4071,11 @@
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3920,8 +4121,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3967,8 +4171,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4014,8 +4221,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4061,8 +4271,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4108,44 +4321,47 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E89" s="3">
         <v>5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>61000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>180200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-56600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>105700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>81300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-71400</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
@@ -4155,8 +4371,11 @@
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4174,46 +4393,47 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-33200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30500</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4221,8 +4441,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4268,8 +4491,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4315,44 +4541,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4362,8 +4591,11 @@
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4381,8 +4613,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4419,8 +4652,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4428,8 +4661,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4475,8 +4711,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4522,8 +4761,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4569,44 +4811,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E100" s="3">
         <v>4300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>59900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-33900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-141800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>86800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>36300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-82000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-52200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>110100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4616,35 +4861,38 @@
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4663,51 +4911,57 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>CTRI</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E7" s="2">
         <v>46019</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="2">
         <v>44927</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44836</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>723200</v>
+      </c>
+      <c r="E8" s="3">
         <v>858600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>850000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>724100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>550100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>717100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>720100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>672100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>528000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>665300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>774900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>805800</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>771900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>758500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>706100</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>687400</v>
+      </c>
+      <c r="E9" s="3">
         <v>778100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>772100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>656300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>529800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>646000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>644300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>611600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>514700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>611400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>687300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>715800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -837,47 +844,50 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E10" s="3">
         <v>80500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>78000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>60500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>53900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>87600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>90000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -887,8 +897,11 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,8 +920,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -957,8 +971,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,49 +1024,52 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>10500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>221400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1057,16 +1077,19 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E15" s="3">
         <v>7200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>6700</v>
       </c>
       <c r="F15" s="3">
         <v>6700</v>
@@ -1096,10 +1119,10 @@
         <v>6700</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
+        <v>6700</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>5</v>
@@ -1107,8 +1130,11 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,47 +1150,48 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>727900</v>
+      </c>
+      <c r="E17" s="3">
         <v>819300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>811400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>691900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>562800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>684000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>676200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>638600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>541600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>639400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>721900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>752600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1174,47 +1201,50 @@
       <c r="R17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E18" s="3">
         <v>39300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>53000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>53200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1224,8 +1254,11 @@
       <c r="R18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,47 +1277,48 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>500</v>
       </c>
       <c r="H20" s="3">
         <v>500</v>
       </c>
       <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1294,49 +1328,52 @@
       <c r="R20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>46900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>50700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>40800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>59700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>60800</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
+      <c r="P21" s="3">
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
@@ -1344,47 +1381,50 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E22" s="3">
         <v>7400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1394,47 +1434,50 @@
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E23" s="3">
         <v>21300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-220200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1444,47 +1487,50 @@
       <c r="R23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-13100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-20800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1494,8 +1540,11 @@
       <c r="R24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,47 +1593,50 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E26" s="3">
         <v>30400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-212800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1594,47 +1646,50 @@
       <c r="R26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
         <v>30200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-210700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17100</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1644,8 +1699,11 @@
       <c r="R27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1752,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1805,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1858,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,47 +1911,50 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-500</v>
       </c>
       <c r="H32" s="3">
         <v>-500</v>
       </c>
       <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1894,47 +1964,50 @@
       <c r="R32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>30200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-210700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17100</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1944,8 +2017,11 @@
       <c r="R33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,47 +2070,50 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>30200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-210700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17100</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2044,63 +2123,69 @@
       <c r="R35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46019</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="P38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="2">
         <v>44927</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44836</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2204,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,41 +2225,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E41" s="3">
         <v>126600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33400</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2189,8 +2276,11 @@
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2239,41 +2329,44 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700900</v>
+      </c>
+      <c r="E43" s="3">
         <v>709800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>671100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>570600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>479700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>519600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>541600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>627300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>545600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>617300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2289,8 +2382,11 @@
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2330,8 +2426,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2339,8 +2435,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2389,41 +2488,44 @@
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>805600</v>
+      </c>
+      <c r="E46" s="3">
         <v>881400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>740500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>651900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>536100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>601400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>634600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>723700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>613000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>682900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2439,49 +2541,52 @@
       <c r="R46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>11500</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>10900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>11900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2489,41 +2594,44 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>664200</v>
+      </c>
+      <c r="E48" s="3">
         <v>667700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>627400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>639900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>640600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>649200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>644100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>685300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>696600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>707400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2539,46 +2647,49 @@
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>728500</v>
+      </c>
+      <c r="E49" s="3">
         <v>738900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>692700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>701500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>702700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>709200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>722600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>727800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>735600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>744900</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
@@ -2589,8 +2700,11 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2753,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,41 +2806,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E52" s="3">
         <v>74400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>84900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>84600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>85800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>76800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>83900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>53400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38500</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2739,8 +2859,11 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,41 +2912,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2321600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2407700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2177300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2107800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1992600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2074400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2112700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2221600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2119300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2189900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>5</v>
       </c>
@@ -2839,8 +2965,11 @@
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +2988,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,41 +3009,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>141600</v>
+      </c>
+      <c r="E57" s="3">
         <v>193600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>146600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>128200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>116000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>125700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>121300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>116600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>116600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,46 +3060,49 @@
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E58" s="3">
         <v>86700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>74200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>68700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>63700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>73200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>69300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>71200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>81900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>86600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
@@ -2979,41 +3113,44 @@
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E59" s="3">
         <v>50500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>109800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3029,41 +3166,44 @@
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>428600</v>
+      </c>
+      <c r="E60" s="3">
         <v>496400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>442200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>379500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>340500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>382300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>386200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>353500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>440200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>420600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3079,41 +3219,44 @@
       <c r="R60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>860200</v>
+      </c>
+      <c r="E61" s="3">
         <v>870800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>995500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>995200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>930300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>950600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>992300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1129000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1272300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1237800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3129,41 +3272,44 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E62" s="3">
         <v>83800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>77100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>65400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>66100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>67900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>69900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>69600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>71100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3179,8 +3325,11 @@
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3378,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3431,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,41 +3484,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1453600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1529300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1587300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1535900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1451400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1514200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1581300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1687200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1917000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1864700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>5</v>
       </c>
@@ -3379,8 +3537,11 @@
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3560,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3611,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3664,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3717,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,41 +3770,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-137900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-128400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-158600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-160700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-168700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-150700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-161000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-157300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-169000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-144100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3649,8 +3823,11 @@
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +3876,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +3929,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,41 +3982,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>862100</v>
+      </c>
+      <c r="E76" s="3">
         <v>873000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>585200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>567100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>536500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>555600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>527300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>530400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>197800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>226000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>5</v>
       </c>
@@ -3849,8 +4035,11 @@
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,102 +4088,108 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E80" s="2">
         <v>46019</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P80" s="2">
+      <c r="P80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="2">
         <v>44927</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44836</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44745</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>30200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-210700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17100</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4004,8 +4199,11 @@
       <c r="R81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,38 +4222,39 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E83" s="3">
         <v>32000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>31800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>32800</v>
       </c>
       <c r="G83" s="3">
         <v>32800</v>
       </c>
       <c r="H83" s="3">
+        <v>32800</v>
+      </c>
+      <c r="I83" s="3">
         <v>32600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4074,8 +4273,11 @@
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4326,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4379,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4432,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4485,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,47 +4538,50 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E89" s="3">
         <v>83900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>61000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>180200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-56600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>105700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>81300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-71400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
@@ -4374,8 +4591,11 @@
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,49 +4614,50 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-33200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30500</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4444,8 +4665,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4718,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,47 +4771,50 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4594,8 +4824,11 @@
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +4847,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4655,8 +4889,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4664,8 +4898,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +4951,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5004,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,47 +5057,50 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E100" s="3">
         <v>51800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>59900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-33900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-141800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>86800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>36300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-82000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-52200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>110100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4864,38 +5110,41 @@
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4914,54 +5163,60 @@
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="E102" s="3">
         <v>111900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10400</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
